--- a/data - Santiago2025/Species traits - TDF - 100925.xlsx
+++ b/data - Santiago2025/Species traits - TDF - 100925.xlsx
@@ -23,7 +23,7 @@
 	-Tomás Ignacio Marina</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H47">
+    <comment authorId="0" ref="H46">
       <text>
         <t xml:space="preserve">creo que necesitamos una categoría intermedia; acá tenés dos bichos uno al lado del otro (Bubo y Theristicus) uno que come una liebre y el otro que no pasa de un anfibio pequeño (que acá no hay encima)
 	-Ulises Balza</t>
@@ -35,7 +35,7 @@
 	-Ulises Balza</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H83">
+    <comment authorId="0" ref="H82">
       <text>
         <t xml:space="preserve">no sé si es correcto, pero no quiero que a un bicho que es exclusivamente ave marina le haga un link con una especie terrestre solo porque es mas chica
 	-Ulises Balza</t>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="346">
   <si>
     <t>Class</t>
   </si>
@@ -356,12 +356,6 @@
   </si>
   <si>
     <t>Ovis_aries</t>
-  </si>
-  <si>
-    <t>Panthera</t>
-  </si>
-  <si>
-    <t>Panthera_onca_mesembrina</t>
   </si>
   <si>
     <t>Phocoenidae</t>
@@ -722,6 +716,12 @@
   </si>
   <si>
     <t>Abrothrix_olivacea</t>
+  </si>
+  <si>
+    <t>Panthera</t>
+  </si>
+  <si>
+    <t>Panthera_onca_mesembrina</t>
   </si>
   <si>
     <t>Reithrodon</t>
@@ -2735,32 +2735,32 @@
         <v>13</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F24" s="5">
-        <v>190.0</v>
+        <v>75.0</v>
       </c>
       <c r="G24" s="5">
-        <v>243.0</v>
+        <v>110.0</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" s="4">
+        <v>62</v>
+      </c>
+      <c r="I24" s="6"/>
+      <c r="J24" s="4">
         <v>1.0</v>
       </c>
-      <c r="J24" s="6"/>
       <c r="K24" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -2786,32 +2786,32 @@
         <v>13</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>87</v>
       </c>
       <c r="F25" s="5">
-        <v>75.0</v>
+        <v>31.0</v>
       </c>
       <c r="G25" s="5">
-        <v>110.0</v>
+        <v>80.0</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="6"/>
-      <c r="J25" s="4">
+        <v>67</v>
+      </c>
+      <c r="I25" s="4">
         <v>1.0</v>
       </c>
+      <c r="J25" s="6"/>
       <c r="K25" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -2849,10 +2849,10 @@
         <v>89</v>
       </c>
       <c r="F26" s="5">
-        <v>31.0</v>
+        <v>220.0</v>
       </c>
       <c r="G26" s="5">
-        <v>80.0</v>
+        <v>360.0</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>67</v>
@@ -2885,35 +2885,33 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F27" s="5">
-        <v>220.0</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="5">
-        <v>360.0</v>
+        <v>7.8</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1.0</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -2939,30 +2937,32 @@
         <v>42</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="5">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="G28" s="5">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I28" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J28" s="6"/>
       <c r="K28" s="4" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -2988,32 +2988,30 @@
         <v>42</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F29" s="5">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="G29" s="5">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I29" s="4">
-        <v>1.0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -3036,25 +3034,25 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F30" s="5">
-        <v>3.4</v>
+        <v>40.0</v>
       </c>
       <c r="G30" s="5">
-        <v>6.5</v>
+        <v>45.0</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>18</v>
@@ -3085,33 +3083,33 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F31" s="5">
-        <v>40.0</v>
+        <v>1.3</v>
       </c>
       <c r="G31" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>18</v>
+        <v>3.0</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
       <c r="K31" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -3137,7 +3135,7 @@
         <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>105</v>
@@ -3149,15 +3147,17 @@
         <v>106</v>
       </c>
       <c r="F32" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G32" s="5">
         <v>1.3</v>
       </c>
-      <c r="G32" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="6"/>
+      <c r="H32" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J32" s="6"/>
       <c r="K32" s="4" t="s">
         <v>29</v>
@@ -3186,22 +3186,20 @@
         <v>42</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" s="4" t="s">
         <v>108</v>
       </c>
+      <c r="D33" s="6"/>
       <c r="E33" s="4" t="s">
         <v>108</v>
       </c>
       <c r="F33" s="5">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G33" s="5">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>67</v>
@@ -3237,30 +3235,28 @@
         <v>42</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="F34" s="5">
         <v>0.4</v>
       </c>
       <c r="G34" s="5">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1.0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -3286,23 +3282,23 @@
         <v>42</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="D35" s="6"/>
       <c r="E35" s="4" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="F35" s="5">
-        <v>0.4</v>
+        <v>15.0</v>
       </c>
       <c r="G35" s="5">
-        <v>6.5</v>
+        <v>25.0</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -3338,23 +3334,25 @@
       <c r="C36" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="5">
-        <v>15.0</v>
-      </c>
-      <c r="G36" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>28</v>
+      <c r="D36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F36" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="G36" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
       <c r="K36" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
@@ -3380,10 +3378,10 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>115</v>
@@ -3392,21 +3390,23 @@
         <v>116</v>
       </c>
       <c r="F37" s="9">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="G37" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>62</v>
+        <v>4.3</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="4" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="M37" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -3429,25 +3429,25 @@
         <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F38" s="9">
-        <v>2.3</v>
+        <v>9.3</v>
       </c>
       <c r="G38" s="9">
-        <v>4.3</v>
+        <v>17.3</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
@@ -3455,9 +3455,7 @@
         <v>63</v>
       </c>
       <c r="L38" s="6"/>
-      <c r="M38" s="4" t="s">
-        <v>119</v>
-      </c>
+      <c r="M38" s="6"/>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
@@ -3480,22 +3478,22 @@
         <v>42</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="F39" s="9">
-        <v>9.3</v>
+        <v>19.0</v>
       </c>
       <c r="G39" s="9">
-        <v>17.3</v>
+        <v>46.0</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>62</v>
@@ -3529,25 +3527,25 @@
         <v>42</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>122</v>
       </c>
       <c r="F40" s="9">
-        <v>19.0</v>
+        <v>4.5</v>
       </c>
       <c r="G40" s="9">
-        <v>46.0</v>
+        <v>8.5</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
@@ -3578,10 +3576,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>123</v>
@@ -3590,15 +3588,17 @@
         <v>124</v>
       </c>
       <c r="F41" s="9">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="G41" s="9">
-        <v>8.5</v>
+        <v>1.7</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I41" s="6"/>
+      <c r="I41" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J41" s="6"/>
       <c r="K41" s="4" t="s">
         <v>63</v>
@@ -3627,32 +3627,30 @@
         <v>42</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="F42" s="9">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="G42" s="9">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I42" s="4">
-        <v>1.0</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="4" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -3678,30 +3676,30 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" s="12" t="s">
         <v>130</v>
       </c>
+      <c r="E43" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="F43" s="9">
-        <v>1.9</v>
+        <v>0.246</v>
       </c>
       <c r="G43" s="9">
-        <v>2.1</v>
+        <v>0.285</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -3727,25 +3725,25 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F44" s="9">
-        <v>0.246</v>
+        <v>0.187</v>
       </c>
       <c r="G44" s="9">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
@@ -3776,22 +3774,22 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" s="9">
-        <v>0.187</v>
+        <v>0.557</v>
       </c>
       <c r="G45" s="9">
-        <v>0.455</v>
+        <v>1.5</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>67</v>
@@ -3825,25 +3823,25 @@
         <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F46" s="9">
-        <v>0.557</v>
+        <v>1.466</v>
       </c>
       <c r="G46" s="9">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
@@ -3874,25 +3872,25 @@
         <v>42</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F47" s="9">
-        <v>1.466</v>
-      </c>
-      <c r="G47" s="9">
-        <v>1.55</v>
+        <v>146</v>
+      </c>
+      <c r="F47" s="13">
+        <v>0.207</v>
+      </c>
+      <c r="G47" s="13">
+        <v>0.4</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
@@ -3923,10 +3921,10 @@
         <v>42</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>147</v>
@@ -3934,16 +3932,18 @@
       <c r="E48" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F48" s="13">
-        <v>0.207</v>
-      </c>
-      <c r="G48" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="H48" s="11" t="s">
+      <c r="F48" s="9">
+        <v>0.289</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I48" s="6"/>
+      <c r="I48" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J48" s="6"/>
       <c r="K48" s="4" t="s">
         <v>19</v>
@@ -3972,10 +3972,10 @@
         <v>42</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>149</v>
@@ -3984,10 +3984,10 @@
         <v>150</v>
       </c>
       <c r="F49" s="9">
-        <v>0.289</v>
+        <v>0.66</v>
       </c>
       <c r="G49" s="9">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>67</v>
@@ -4022,23 +4022,23 @@
       <c r="A50" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>145</v>
+      <c r="B50" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="F50" s="9">
-        <v>0.66</v>
+        <v>1.67</v>
       </c>
       <c r="G50" s="9">
-        <v>1.3</v>
+        <v>3.17</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>67</v>
@@ -4073,23 +4073,23 @@
       <c r="A51" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>145</v>
+      <c r="B51" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>153</v>
       </c>
       <c r="F51" s="9">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="G51" s="9">
-        <v>3.17</v>
+        <v>1.6</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>67</v>
@@ -4125,32 +4125,32 @@
         <v>42</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F52" s="9">
-        <v>1.15</v>
+        <v>2.84</v>
       </c>
       <c r="G52" s="9">
-        <v>1.6</v>
+        <v>4.658</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I52" s="4">
         <v>1.0</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
@@ -4176,32 +4176,30 @@
         <v>42</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F53" s="9">
-        <v>2.84</v>
+        <v>0.485</v>
       </c>
       <c r="G53" s="9">
-        <v>4.658</v>
+        <v>1.5</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I53" s="4">
-        <v>1.0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
@@ -4227,10 +4225,10 @@
         <v>42</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>162</v>
@@ -4239,13 +4237,13 @@
         <v>163</v>
       </c>
       <c r="F54" s="9">
-        <v>0.485</v>
+        <v>0.3</v>
       </c>
       <c r="G54" s="9">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
@@ -4276,25 +4274,25 @@
         <v>42</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F55" s="9">
-        <v>0.3</v>
+        <v>0.276</v>
       </c>
       <c r="G55" s="9">
-        <v>0.5</v>
+        <v>0.363</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
@@ -4325,10 +4323,10 @@
         <v>42</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>168</v>
@@ -4337,18 +4335,18 @@
         <v>169</v>
       </c>
       <c r="F56" s="9">
-        <v>0.276</v>
+        <v>1.72</v>
       </c>
       <c r="G56" s="9">
-        <v>0.363</v>
+        <v>2.72</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
@@ -4374,22 +4372,22 @@
         <v>42</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="F57" s="9">
         <v>1.72</v>
       </c>
       <c r="G57" s="9">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>62</v>
@@ -4423,10 +4421,10 @@
         <v>42</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>106</v>
@@ -4435,15 +4433,17 @@
         <v>172</v>
       </c>
       <c r="F58" s="9">
-        <v>1.72</v>
+        <v>0.28</v>
       </c>
       <c r="G58" s="9">
-        <v>2.3</v>
+        <v>0.36</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="I58" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J58" s="6"/>
       <c r="K58" s="4" t="s">
         <v>29</v>
@@ -4472,25 +4472,25 @@
         <v>42</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>174</v>
       </c>
       <c r="F59" s="9">
-        <v>0.28</v>
+        <v>0.278</v>
       </c>
       <c r="G59" s="9">
-        <v>0.36</v>
+        <v>1.1</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I59" s="4">
         <v>1.0</v>
@@ -4523,10 +4523,10 @@
         <v>42</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>175</v>
@@ -4535,20 +4535,18 @@
         <v>176</v>
       </c>
       <c r="F60" s="9">
-        <v>0.278</v>
+        <v>2.84</v>
       </c>
       <c r="G60" s="9">
-        <v>1.1</v>
+        <v>4.658</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I60" s="4">
-        <v>1.0</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="4" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
@@ -4574,27 +4572,29 @@
         <v>42</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F61" s="9">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="G61" s="9">
-        <v>4.658</v>
+        <v>5.0</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="I61" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J61" s="6"/>
       <c r="K61" s="4" t="s">
         <v>63</v>
@@ -4623,10 +4623,10 @@
         <v>42</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>180</v>
@@ -4635,20 +4635,18 @@
         <v>181</v>
       </c>
       <c r="F62" s="9">
-        <v>3.8</v>
+        <v>0.388</v>
       </c>
       <c r="G62" s="9">
-        <v>5.0</v>
+        <v>0.83</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I62" s="4">
-        <v>1.0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
@@ -4680,16 +4678,16 @@
         <v>44</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>183</v>
-      </c>
       <c r="F63" s="9">
-        <v>0.388</v>
+        <v>0.9</v>
       </c>
       <c r="G63" s="9">
-        <v>0.83</v>
+        <v>1.4</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>28</v>
@@ -4700,7 +4698,9 @@
         <v>19</v>
       </c>
       <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
+      <c r="M63" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
@@ -4729,16 +4729,16 @@
         <v>44</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>184</v>
       </c>
       <c r="F64" s="9">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="G64" s="9">
-        <v>1.4</v>
+        <v>0.655</v>
       </c>
       <c r="H64" s="8" t="s">
         <v>28</v>
@@ -4749,9 +4749,7 @@
         <v>19</v>
       </c>
       <c r="L64" s="6"/>
-      <c r="M64" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="M64" s="6"/>
       <c r="N64" s="6"/>
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
@@ -4774,25 +4772,25 @@
         <v>42</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" s="9">
-        <v>0.46</v>
-      </c>
-      <c r="G65" s="9">
-        <v>0.655</v>
+        <v>187</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0.308</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0.35</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
@@ -4823,10 +4821,10 @@
         <v>42</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>188</v>
@@ -4834,14 +4832,14 @@
       <c r="E66" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F66" s="14">
-        <v>0.308</v>
-      </c>
-      <c r="G66" s="14">
-        <v>0.35</v>
+      <c r="F66" s="9">
+        <v>0.206</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0.363</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
@@ -4872,30 +4870,32 @@
         <v>42</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F67" s="9">
-        <v>0.206</v>
+        <v>2.84</v>
       </c>
       <c r="G67" s="9">
-        <v>0.363</v>
-      </c>
-      <c r="H67" s="8" t="s">
+        <v>5.0</v>
+      </c>
+      <c r="H67" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I67" s="6"/>
+      <c r="I67" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J67" s="6"/>
       <c r="K67" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
@@ -4921,29 +4921,27 @@
         <v>42</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F68" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="G68" s="9">
-        <v>5.0</v>
+        <v>115</v>
+      </c>
+      <c r="F68" s="14">
+        <v>2.3</v>
+      </c>
+      <c r="G68" s="14">
+        <v>4.3</v>
       </c>
       <c r="H68" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I68" s="4">
-        <v>1.0</v>
-      </c>
+      <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="4" t="s">
         <v>63</v>
@@ -4972,22 +4970,20 @@
         <v>42</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>117</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D69" s="4"/>
       <c r="E69" s="7" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F69" s="14">
         <v>2.3</v>
       </c>
       <c r="G69" s="14">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>67</v>
@@ -5021,28 +5017,28 @@
         <v>42</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F70" s="14">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="G70" s="14">
-        <v>7.8</v>
+        <v>3.0</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="4" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
@@ -5068,28 +5064,30 @@
         <v>42</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="E71" s="7" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="F71" s="14">
-        <v>1.3</v>
+        <v>2.47</v>
       </c>
       <c r="G71" s="14">
-        <v>3.0</v>
+        <v>3.56</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
       <c r="K71" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
@@ -5115,30 +5113,30 @@
         <v>42</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>45</v>
+        <v>171</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="F72" s="14">
-        <v>2.47</v>
+        <v>0.8</v>
       </c>
       <c r="G72" s="14">
-        <v>3.56</v>
+        <v>1.3</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="I72" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="K72" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
@@ -5164,30 +5162,26 @@
         <v>42</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="F73" s="14">
-        <v>0.8</v>
+        <v>0.187</v>
       </c>
       <c r="G73" s="14">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I73" s="4">
-        <v>1.0</v>
-      </c>
+      <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
@@ -5213,23 +5207,27 @@
         <v>42</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C74" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="D74" s="4"/>
-      <c r="E74" s="4" t="s">
-        <v>134</v>
+      <c r="E74" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="F74" s="14">
-        <v>0.187</v>
+        <v>0.207</v>
       </c>
       <c r="G74" s="14">
-        <v>1.5</v>
+        <v>3.17</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I74" s="6"/>
+      <c r="I74" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J74" s="6"/>
       <c r="K74" s="4" t="s">
         <v>19</v>
@@ -5258,27 +5256,23 @@
         <v>42</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>146</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="7" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="F75" s="14">
-        <v>0.207</v>
+        <v>0.246</v>
       </c>
       <c r="G75" s="14">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I75" s="4">
-        <v>1.0</v>
-      </c>
+      <c r="I75" s="6"/>
       <c r="J75" s="6"/>
       <c r="K75" s="4" t="s">
         <v>19</v>
@@ -5307,26 +5301,32 @@
         <v>42</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F76" s="14">
-        <v>0.246</v>
-      </c>
-      <c r="G76" s="14">
-        <v>1.7</v>
+        <v>154</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" s="9">
+        <v>2.84</v>
+      </c>
+      <c r="G76" s="9">
+        <v>5.0</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I76" s="6"/>
+      <c r="I76" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J76" s="6"/>
       <c r="K76" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
@@ -5352,32 +5352,26 @@
         <v>42</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F77" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="G77" s="9">
-        <v>5.0</v>
+        <v>190</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="G77" s="14">
+        <v>1.0</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I77" s="4">
-        <v>1.0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I77" s="6"/>
       <c r="J77" s="6"/>
       <c r="K77" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
@@ -5403,21 +5397,23 @@
         <v>42</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C78" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="D78" s="4"/>
       <c r="E78" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F78" s="14">
-        <v>0.04</v>
+        <v>0.585</v>
       </c>
       <c r="G78" s="14">
-        <v>1.0</v>
+        <v>0.85</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
@@ -5448,28 +5444,28 @@
         <v>42</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>193</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F79" s="14">
-        <v>0.585</v>
-      </c>
-      <c r="G79" s="14">
-        <v>0.85</v>
+        <v>154</v>
+      </c>
+      <c r="F79" s="9">
+        <v>2.84</v>
+      </c>
+      <c r="G79" s="9">
+        <v>5.0</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I79" s="6"/>
+      <c r="I79" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J79" s="6"/>
       <c r="K79" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -5495,18 +5491,22 @@
         <v>42</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="E80" s="7" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="F80" s="9">
-        <v>2.84</v>
+        <v>0.81</v>
       </c>
       <c r="G80" s="9">
-        <v>5.0</v>
+        <v>1.335</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>67</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J80" s="6"/>
       <c r="K80" s="4" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
@@ -5542,35 +5542,35 @@
         <v>42</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F81" s="9">
-        <v>0.81</v>
-      </c>
-      <c r="G81" s="9">
-        <v>1.335</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I81" s="4">
+      <c r="F81" s="5">
         <v>1.0</v>
       </c>
+      <c r="G81" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="6"/>
       <c r="J81" s="6"/>
       <c r="K81" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
+      <c r="M81" s="4" t="s">
+        <v>196</v>
+      </c>
       <c r="N81" s="6"/>
       <c r="O81" s="6"/>
       <c r="P81" s="6"/>
@@ -5593,35 +5593,33 @@
         <v>42</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F82" s="5">
-        <v>1.0</v>
+        <v>0.2</v>
       </c>
       <c r="G82" s="5">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
       <c r="K82" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L82" s="6"/>
-      <c r="M82" s="4" t="s">
-        <v>198</v>
-      </c>
+      <c r="M82" s="6"/>
       <c r="N82" s="6"/>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
@@ -5641,28 +5639,24 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F83" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="G83" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>62</v>
+      <c r="F83" s="14">
+        <v>40.0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>3996.0</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
@@ -5693,26 +5687,30 @@
         <v>13</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F84" s="14">
-        <v>40.0</v>
-      </c>
-      <c r="G84" s="14">
-        <v>3996.0</v>
-      </c>
-      <c r="H84" s="11" t="s">
-        <v>67</v>
+      <c r="F84" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G84" s="5">
+        <v>0.022</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
       <c r="K84" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
@@ -5744,16 +5742,16 @@
         <v>31</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="F85" s="5">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="G85" s="5">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>28</v>
@@ -5783,29 +5781,29 @@
       <c r="AC85" s="6"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" s="4" t="s">
+      <c r="B86" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>205</v>
       </c>
       <c r="F86" s="5">
-        <v>0.012</v>
+        <v>50.0</v>
       </c>
       <c r="G86" s="5">
-        <v>0.024</v>
+        <v>200.0</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
@@ -5832,29 +5830,29 @@
       <c r="AC86" s="6"/>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B87" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>85</v>
+      <c r="B87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="F87" s="5">
-        <v>50.0</v>
+        <v>0.052</v>
       </c>
       <c r="G87" s="5">
-        <v>129.0</v>
+        <v>0.116</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
@@ -5885,30 +5883,30 @@
         <v>13</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F88" s="5">
-        <v>0.052</v>
+        <v>40.0</v>
       </c>
       <c r="G88" s="5">
-        <v>0.116</v>
+        <v>160.0</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
@@ -5937,19 +5935,19 @@
         <v>38</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F89" s="5">
-        <v>40.0</v>
+        <v>400.0</v>
       </c>
       <c r="G89" s="5">
-        <v>160.0</v>
+        <v>3996.0</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>67</v>
@@ -5983,28 +5981,30 @@
         <v>13</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>38</v>
+        <v>213</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F90" s="5">
-        <v>400.0</v>
+        <v>20000.0</v>
       </c>
       <c r="G90" s="5">
-        <v>3996.0</v>
+        <v>22000.0</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
+      <c r="J90" s="4">
+        <v>1.0</v>
+      </c>
       <c r="K90" s="4" t="s">
         <v>63</v>
       </c>
@@ -6035,19 +6035,19 @@
         <v>213</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F91" s="5">
         <v>20000.0</v>
       </c>
       <c r="G91" s="5">
-        <v>22000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>67</v>
@@ -6086,19 +6086,19 @@
         <v>213</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F92" s="5">
-        <v>20000.0</v>
+        <v>380.0</v>
       </c>
       <c r="G92" s="5">
-        <v>50000.0</v>
+        <v>500.0</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>67</v>
@@ -6134,32 +6134,30 @@
         <v>13</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F93" s="5">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
       <c r="G93" s="5">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="I93" s="6"/>
-      <c r="J93" s="4">
-        <v>1.0</v>
-      </c>
+      <c r="J93" s="6"/>
       <c r="K93" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
@@ -6188,21 +6186,19 @@
         <v>14</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>223</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D94" s="4"/>
       <c r="E94" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F94" s="5">
-        <v>400.0</v>
-      </c>
-      <c r="G94" s="5">
-        <v>1000.0</v>
-      </c>
-      <c r="H94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F94" s="14">
+        <v>40.0</v>
+      </c>
+      <c r="G94" s="14">
+        <v>98.0</v>
+      </c>
+      <c r="H94" s="11" t="s">
         <v>18</v>
       </c>
       <c r="I94" s="6"/>
@@ -6234,23 +6230,21 @@
         <v>13</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F95" s="14">
-        <v>40.0</v>
+        <v>0.02</v>
       </c>
       <c r="G95" s="14">
-        <v>98.0</v>
+        <v>5.5</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
@@ -6281,21 +6275,21 @@
         <v>13</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="F96" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="G96" s="14">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
@@ -6326,26 +6320,30 @@
         <v>13</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="E97" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F97" s="14">
-        <v>0.1</v>
+        <v>6.0</v>
       </c>
       <c r="G97" s="14">
-        <v>2.5</v>
+        <v>15.0</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
@@ -6374,16 +6372,14 @@
         <v>38</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>226</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D98" s="4"/>
       <c r="E98" s="4" t="s">
-        <v>226</v>
+        <v>50</v>
       </c>
       <c r="F98" s="14">
-        <v>6.0</v>
+        <v>3.8</v>
       </c>
       <c r="G98" s="14">
         <v>15.0</v>
@@ -6394,7 +6390,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
@@ -6423,17 +6419,17 @@
         <v>38</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F99" s="14">
-        <v>3.8</v>
+        <v>237.0</v>
       </c>
       <c r="G99" s="14">
-        <v>15.0</v>
+        <v>3996.0</v>
       </c>
       <c r="H99" s="11" t="s">
         <v>67</v>
@@ -6441,7 +6437,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
       <c r="K99" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
@@ -6467,20 +6463,20 @@
         <v>13</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>59</v>
+        <v>14</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>220</v>
       </c>
       <c r="D100" s="4"/>
-      <c r="E100" s="4" t="s">
-        <v>59</v>
+      <c r="E100" s="16" t="s">
+        <v>220</v>
       </c>
       <c r="F100" s="14">
-        <v>237.0</v>
+        <v>380.0</v>
       </c>
       <c r="G100" s="14">
-        <v>3996.0</v>
+        <v>500.0</v>
       </c>
       <c r="H100" s="11" t="s">
         <v>67</v>
@@ -6516,18 +6512,16 @@
       <c r="B101" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C101" s="15" t="s">
-        <v>220</v>
-      </c>
+      <c r="C101" s="4"/>
       <c r="D101" s="4"/>
-      <c r="E101" s="16" t="s">
-        <v>220</v>
+      <c r="E101" s="4" t="s">
+        <v>227</v>
       </c>
       <c r="F101" s="14">
-        <v>380.0</v>
+        <v>75.0</v>
       </c>
       <c r="G101" s="14">
-        <v>500.0</v>
+        <v>22000.0</v>
       </c>
       <c r="H101" s="11" t="s">
         <v>67</v>
@@ -6558,24 +6552,28 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
+        <v>229</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>231</v>
+      </c>
       <c r="E102" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F102" s="14">
-        <v>75.0</v>
+        <v>0.012</v>
       </c>
       <c r="G102" s="14">
-        <v>22000.0</v>
+        <v>0.0255</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
@@ -6612,16 +6610,16 @@
         <v>230</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F103" s="14">
-        <v>0.012</v>
+        <v>0.0168</v>
       </c>
       <c r="G103" s="14">
-        <v>0.0255</v>
+        <v>0.045</v>
       </c>
       <c r="H103" s="11" t="s">
         <v>233</v>
@@ -6652,28 +6650,26 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B104" s="4"/>
       <c r="C104" s="4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F104" s="14">
-        <v>0.0168</v>
+        <v>0.007</v>
       </c>
       <c r="G104" s="14">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>233</v>
+        <v>67</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
@@ -6703,21 +6699,23 @@
       <c r="A105" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="4"/>
+      <c r="B105" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="C105" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F105" s="14">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="G105" s="14">
-        <v>0.037</v>
+        <v>0.075</v>
       </c>
       <c r="H105" s="11" t="s">
         <v>67</v>
@@ -6748,28 +6746,28 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F106" s="14">
-        <v>0.003</v>
+        <v>0.0127</v>
       </c>
       <c r="G106" s="14">
-        <v>0.075</v>
+        <v>0.0552</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
@@ -6800,22 +6798,22 @@
         <v>228</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F107" s="14">
-        <v>0.0127</v>
+        <v>0.03</v>
       </c>
       <c r="G107" s="14">
-        <v>0.0552</v>
+        <v>0.103</v>
       </c>
       <c r="H107" s="11" t="s">
         <v>233</v>
@@ -6849,25 +6847,25 @@
         <v>228</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F108" s="14">
-        <v>0.03</v>
+        <v>8.0E-5</v>
       </c>
       <c r="G108" s="14">
-        <v>0.103</v>
+        <v>1.03E-4</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>233</v>
+        <v>28</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
@@ -6895,30 +6893,26 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>251</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B109" s="6"/>
       <c r="C109" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="F109" s="14">
-        <v>8.0E-5</v>
-      </c>
-      <c r="G109" s="14">
-        <v>1.03E-4</v>
-      </c>
-      <c r="H109" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I109" s="6"/>
+        <v>257</v>
+      </c>
+      <c r="F109" s="17"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I109" s="4">
+        <v>1.0</v>
+      </c>
       <c r="J109" s="6"/>
       <c r="K109" s="4" t="s">
         <v>63</v>
@@ -6954,7 +6948,7 @@
         <v>256</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
@@ -6991,24 +6985,24 @@
       <c r="A111" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B111" s="6"/>
+      <c r="B111" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="C111" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F111" s="17"/>
       <c r="G111" s="17"/>
       <c r="H111" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I111" s="4">
-        <v>1.0</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="I111" s="6"/>
       <c r="J111" s="6"/>
       <c r="K111" s="4" t="s">
         <v>63</v>
@@ -7034,23 +7028,23 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F112" s="17"/>
-      <c r="G112" s="17"/>
-      <c r="H112" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="11" t="s">
         <v>262</v>
       </c>
       <c r="I112" s="6"/>
@@ -7088,15 +7082,15 @@
         <v>248</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
+        <v>267</v>
+      </c>
+      <c r="F113" s="17"/>
+      <c r="G113" s="17"/>
       <c r="H113" s="11" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
@@ -7124,24 +7118,28 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
+        <v>272</v>
+      </c>
+      <c r="F114" s="14">
+        <v>0.1833</v>
+      </c>
+      <c r="G114" s="14">
+        <v>0.2003</v>
+      </c>
       <c r="H114" s="11" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
@@ -7169,33 +7167,27 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>269</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B115" s="6"/>
       <c r="C115" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="F115" s="14">
-        <v>0.1833</v>
-      </c>
-      <c r="G115" s="14">
-        <v>0.2003</v>
-      </c>
-      <c r="H115" s="11" t="s">
-        <v>18</v>
+        <v>275</v>
+      </c>
+      <c r="F115" s="17"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
       <c r="K115" s="4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
@@ -7220,25 +7212,31 @@
       <c r="A116" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B116" s="6"/>
+      <c r="B116" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="C116" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F116" s="17"/>
-      <c r="G116" s="17"/>
-      <c r="H116" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="F116" s="14">
+        <v>0.07</v>
+      </c>
+      <c r="G116" s="14">
+        <v>0.28</v>
+      </c>
+      <c r="H116" s="11" t="s">
         <v>67</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
       <c r="K116" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
@@ -7263,26 +7261,24 @@
       <c r="A117" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>240</v>
-      </c>
+      <c r="B117" s="6"/>
       <c r="C117" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F117" s="14">
-        <v>0.07</v>
+        <v>0.00339</v>
       </c>
       <c r="G117" s="14">
-        <v>0.28</v>
+        <v>0.0078</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
@@ -7312,24 +7308,26 @@
       <c r="A118" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B118" s="6"/>
+      <c r="B118" s="4" t="s">
+        <v>240</v>
+      </c>
       <c r="C118" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F118" s="14">
-        <v>0.00339</v>
+        <v>0.3</v>
       </c>
       <c r="G118" s="14">
-        <v>0.0078</v>
+        <v>4.0</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
@@ -7359,28 +7357,25 @@
       <c r="A119" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="4" t="s">
-        <v>240</v>
-      </c>
+      <c r="B119" s="6"/>
       <c r="C119" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F119" s="14">
-        <v>0.3</v>
+        <v>282</v>
+      </c>
+      <c r="F119" s="5">
+        <v>0.0095</v>
       </c>
       <c r="G119" s="14">
-        <v>4.0</v>
+        <v>0.0181</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I119" s="6"/>
+        <v>28</v>
+      </c>
       <c r="J119" s="6"/>
       <c r="K119" s="4" t="s">
         <v>63</v>
@@ -7406,27 +7401,26 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="B120" s="6"/>
-      <c r="C120" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="F120" s="5">
-        <v>0.0095</v>
+      <c r="C120" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D120" s="6"/>
+      <c r="E120" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F120" s="14">
+        <v>0.0033</v>
       </c>
       <c r="G120" s="14">
-        <v>0.0181</v>
+        <v>0.0219</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="I120" s="6"/>
       <c r="J120" s="6"/>
       <c r="K120" s="4" t="s">
         <v>63</v>
@@ -7452,24 +7446,24 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B121" s="6"/>
-      <c r="C121" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="D121" s="6"/>
-      <c r="E121" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="F121" s="14">
-        <v>0.0033</v>
-      </c>
-      <c r="G121" s="14">
-        <v>0.0219</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F121" s="17"/>
+      <c r="G121" s="17"/>
       <c r="H121" s="11" t="s">
-        <v>28</v>
+        <v>233</v>
       </c>
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
@@ -7497,32 +7491,38 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="F122" s="17"/>
-      <c r="G122" s="17"/>
-      <c r="H122" s="11" t="s">
-        <v>233</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="F122" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G122" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="H122" s="19"/>
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
       <c r="K122" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L122" s="6"/>
-      <c r="M122" s="6"/>
+      <c r="L122" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="M122" s="21" t="s">
+        <v>295</v>
+      </c>
       <c r="N122" s="6"/>
       <c r="O122" s="6"/>
       <c r="P122" s="6"/>
@@ -7545,35 +7545,27 @@
         <v>289</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="F123" s="9">
-        <v>10.0</v>
-      </c>
-      <c r="G123" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="H123" s="19"/>
+        <v>299</v>
+      </c>
+      <c r="F123" s="17"/>
+      <c r="G123" s="17"/>
+      <c r="H123" s="18"/>
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
       <c r="K123" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L123" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="M123" s="21" t="s">
-        <v>295</v>
-      </c>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
       <c r="N123" s="6"/>
       <c r="O123" s="6"/>
       <c r="P123" s="6"/>
@@ -7599,24 +7591,32 @@
         <v>296</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="F124" s="17"/>
-      <c r="G124" s="17"/>
-      <c r="H124" s="18"/>
+        <v>302</v>
+      </c>
+      <c r="F124" s="9">
+        <v>0.052</v>
+      </c>
+      <c r="G124" s="9">
+        <v>1.57</v>
+      </c>
+      <c r="H124" s="19"/>
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
       <c r="K124" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L124" s="6"/>
-      <c r="M124" s="6"/>
+      <c r="L124" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="M124" s="4" t="s">
+        <v>303</v>
+      </c>
       <c r="N124" s="6"/>
       <c r="O124" s="6"/>
       <c r="P124" s="6"/>
@@ -7639,22 +7639,22 @@
         <v>289</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F125" s="9">
-        <v>0.052</v>
+        <v>0.5</v>
       </c>
       <c r="G125" s="9">
-        <v>1.57</v>
+        <v>5.0</v>
       </c>
       <c r="H125" s="19"/>
       <c r="I125" s="6"/>
@@ -7662,11 +7662,9 @@
       <c r="K125" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L125" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="M125" s="4" t="s">
-        <v>303</v>
+      <c r="L125" s="6"/>
+      <c r="M125" s="21" t="s">
+        <v>294</v>
       </c>
       <c r="N125" s="6"/>
       <c r="O125" s="6"/>
@@ -7690,19 +7688,19 @@
         <v>289</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F126" s="9">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="G126" s="9">
         <v>5.0</v>
@@ -7739,22 +7737,22 @@
         <v>289</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F127" s="9">
-        <v>1.0</v>
+        <v>313</v>
+      </c>
+      <c r="F127" s="23">
+        <v>100.0</v>
       </c>
       <c r="G127" s="9">
-        <v>5.0</v>
+        <v>2.46</v>
       </c>
       <c r="H127" s="19"/>
       <c r="I127" s="6"/>
@@ -7763,9 +7761,7 @@
         <v>63</v>
       </c>
       <c r="L127" s="6"/>
-      <c r="M127" s="21" t="s">
-        <v>294</v>
-      </c>
+      <c r="M127" s="6"/>
       <c r="N127" s="6"/>
       <c r="O127" s="6"/>
       <c r="P127" s="6"/>
@@ -7788,22 +7784,22 @@
         <v>289</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F128" s="23">
-        <v>100.0</v>
+        <v>317</v>
+      </c>
+      <c r="F128" s="9">
+        <v>1.0</v>
       </c>
       <c r="G128" s="9">
-        <v>2.46</v>
+        <v>3.0</v>
       </c>
       <c r="H128" s="19"/>
       <c r="I128" s="6"/>
@@ -7812,7 +7808,9 @@
         <v>63</v>
       </c>
       <c r="L128" s="6"/>
-      <c r="M128" s="6"/>
+      <c r="M128" s="4" t="s">
+        <v>318</v>
+      </c>
       <c r="N128" s="6"/>
       <c r="O128" s="6"/>
       <c r="P128" s="6"/>
@@ -7835,22 +7833,22 @@
         <v>289</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F129" s="9">
-        <v>1.0</v>
+        <v>0.04</v>
       </c>
       <c r="G129" s="9">
-        <v>3.0</v>
+        <v>0.22</v>
       </c>
       <c r="H129" s="19"/>
       <c r="I129" s="6"/>
@@ -7859,9 +7857,7 @@
         <v>63</v>
       </c>
       <c r="L129" s="6"/>
-      <c r="M129" s="4" t="s">
-        <v>318</v>
-      </c>
+      <c r="M129" s="6"/>
       <c r="N129" s="6"/>
       <c r="O129" s="6"/>
       <c r="P129" s="6"/>
@@ -7884,22 +7880,22 @@
         <v>289</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F130" s="9">
-        <v>0.04</v>
+        <v>0.7</v>
       </c>
       <c r="G130" s="9">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="H130" s="19"/>
       <c r="I130" s="6"/>
@@ -7908,7 +7904,9 @@
         <v>63</v>
       </c>
       <c r="L130" s="6"/>
-      <c r="M130" s="6"/>
+      <c r="M130" s="21" t="s">
+        <v>294</v>
+      </c>
       <c r="N130" s="6"/>
       <c r="O130" s="6"/>
       <c r="P130" s="6"/>
@@ -7931,22 +7929,22 @@
         <v>289</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F131" s="9">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G131" s="9">
-        <v>0.85</v>
+        <v>1.5</v>
       </c>
       <c r="H131" s="19"/>
       <c r="I131" s="6"/>
@@ -7983,19 +7981,19 @@
         <v>296</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F132" s="9">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="9">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H132" s="19"/>
       <c r="I132" s="6"/>
@@ -8004,9 +8002,7 @@
         <v>63</v>
       </c>
       <c r="L132" s="6"/>
-      <c r="M132" s="21" t="s">
-        <v>294</v>
-      </c>
+      <c r="M132" s="6"/>
       <c r="N132" s="6"/>
       <c r="O132" s="6"/>
       <c r="P132" s="6"/>
@@ -8032,19 +8028,19 @@
         <v>296</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F133" s="9">
-        <v>0.1</v>
+        <v>0.714</v>
       </c>
       <c r="G133" s="9">
-        <v>1.6</v>
+        <v>6.163</v>
       </c>
       <c r="H133" s="19"/>
       <c r="I133" s="6"/>
@@ -8076,22 +8072,20 @@
         <v>289</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>333</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="D134" s="6"/>
       <c r="E134" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F134" s="9">
-        <v>0.714</v>
+        <v>1.5</v>
       </c>
       <c r="G134" s="9">
-        <v>6.163</v>
+        <v>8.0</v>
       </c>
       <c r="H134" s="19"/>
       <c r="I134" s="6"/>
@@ -8120,23 +8114,25 @@
     </row>
     <row r="135">
       <c r="A135" s="4" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D135" s="6"/>
+        <v>337</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="E135" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F135" s="9">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
       <c r="G135" s="9">
-        <v>8.0</v>
+        <v>0.52</v>
       </c>
       <c r="H135" s="19"/>
       <c r="I135" s="6"/>
@@ -8165,25 +8161,23 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>338</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F136" s="9">
-        <v>0.26</v>
+        <v>0.101</v>
       </c>
       <c r="G136" s="9">
-        <v>0.52</v>
+        <v>0.346</v>
       </c>
       <c r="H136" s="19"/>
       <c r="I136" s="6"/>
@@ -8191,8 +8185,12 @@
       <c r="K136" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
+      <c r="L136" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="M136" s="21" t="s">
+        <v>294</v>
+      </c>
       <c r="N136" s="6"/>
       <c r="O136" s="6"/>
       <c r="P136" s="6"/>
@@ -8220,15 +8218,17 @@
       <c r="C137" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D137" s="4"/>
+      <c r="D137" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="E137" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="F137" s="9">
-        <v>0.101</v>
+        <v>0.0015</v>
       </c>
       <c r="G137" s="9">
-        <v>0.346</v>
+        <v>0.0039</v>
       </c>
       <c r="H137" s="19"/>
       <c r="I137" s="6"/>
@@ -8236,12 +8236,8 @@
       <c r="K137" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L137" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="M137" s="21" t="s">
-        <v>294</v>
-      </c>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
       <c r="N137" s="6"/>
       <c r="O137" s="6"/>
       <c r="P137" s="6"/>
@@ -8261,27 +8257,19 @@
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>339</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
       <c r="E138" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="F138" s="9">
-        <v>0.0015</v>
-      </c>
-      <c r="G138" s="9">
-        <v>0.0039</v>
-      </c>
-      <c r="H138" s="19"/>
+        <v>341</v>
+      </c>
+      <c r="F138" s="17"/>
+      <c r="G138" s="17"/>
+      <c r="H138" s="18"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
       <c r="K138" s="4" t="s">
@@ -8307,25 +8295,17 @@
       <c r="AC138" s="6"/>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>341</v>
-      </c>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
-      <c r="E139" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F139" s="17"/>
-      <c r="G139" s="17"/>
-      <c r="H139" s="18"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="6"/>
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
-      <c r="K139" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="K139" s="6"/>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
       <c r="N139" s="6"/>
@@ -8443,7 +8423,6 @@
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
       <c r="F143" s="24"/>
       <c r="G143" s="24"/>
       <c r="H143" s="6"/>
@@ -8474,6 +8453,7 @@
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
       <c r="F144" s="24"/>
       <c r="G144" s="24"/>
       <c r="H144" s="6"/>
@@ -36802,47 +36782,16 @@
       <c r="AB1057" s="6"/>
       <c r="AC1057" s="6"/>
     </row>
-    <row r="1058">
-      <c r="A1058" s="6"/>
-      <c r="B1058" s="6"/>
-      <c r="C1058" s="6"/>
-      <c r="D1058" s="6"/>
-      <c r="E1058" s="6"/>
-      <c r="F1058" s="24"/>
-      <c r="G1058" s="24"/>
-      <c r="H1058" s="6"/>
-      <c r="I1058" s="6"/>
-      <c r="J1058" s="6"/>
-      <c r="K1058" s="6"/>
-      <c r="L1058" s="6"/>
-      <c r="M1058" s="6"/>
-      <c r="N1058" s="6"/>
-      <c r="O1058" s="6"/>
-      <c r="P1058" s="6"/>
-      <c r="Q1058" s="6"/>
-      <c r="R1058" s="6"/>
-      <c r="S1058" s="6"/>
-      <c r="T1058" s="6"/>
-      <c r="U1058" s="6"/>
-      <c r="V1058" s="6"/>
-      <c r="W1058" s="6"/>
-      <c r="X1058" s="6"/>
-      <c r="Y1058" s="6"/>
-      <c r="Z1058" s="6"/>
-      <c r="AA1058" s="6"/>
-      <c r="AB1058" s="6"/>
-      <c r="AC1058" s="6"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="L123"/>
-    <hyperlink r:id="rId3" ref="M123"/>
-    <hyperlink r:id="rId4" ref="M126"/>
-    <hyperlink r:id="rId5" ref="M127"/>
-    <hyperlink r:id="rId6" ref="M131"/>
-    <hyperlink r:id="rId7" ref="M132"/>
-    <hyperlink r:id="rId8" ref="L137"/>
-    <hyperlink r:id="rId9" ref="M137"/>
+    <hyperlink r:id="rId2" ref="L122"/>
+    <hyperlink r:id="rId3" ref="M122"/>
+    <hyperlink r:id="rId4" ref="M125"/>
+    <hyperlink r:id="rId5" ref="M126"/>
+    <hyperlink r:id="rId6" ref="M130"/>
+    <hyperlink r:id="rId7" ref="M131"/>
+    <hyperlink r:id="rId8" ref="L136"/>
+    <hyperlink r:id="rId9" ref="M136"/>
   </hyperlinks>
   <drawing r:id="rId10"/>
   <legacyDrawing r:id="rId11"/>
